--- a/docs/downloads/AAU_Research_Tracker.xlsx
+++ b/docs/downloads/AAU_Research_Tracker.xlsx
@@ -467,7 +467,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20260831-092219</t>
+          <t>20260907-075752</t>
         </is>
       </c>
     </row>
@@ -479,7 +479,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-31T09:22:29</t>
+          <t>2026-09-07T07:58:00</t>
         </is>
       </c>
     </row>
